--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
@@ -2993,7 +2993,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T16:16:07.933Z</t>
+    <t>2026-10-11T16:44:58.563Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
@@ -2993,7 +2993,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T16:44:58.563Z</t>
+    <t>2026-10-11T17:07:27.843Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
@@ -97,7 +97,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Functional</t>
+    <t>Hotel booking baseline · DQE</t>
   </si>
   <si>
     <t>Baseline</t>
@@ -2984,7 +2984,7 @@
     <t>Agentic QE Platform - MVP</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Functional (CYC-2)</t>
+    <t>Hotel booking baseline · DQE (CYC-2)</t>
   </si>
   <si>
     <t>BL-2 v1</t>
@@ -2993,7 +2993,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T17:07:27.843Z</t>
+    <t>2026-10-12T01:35:49.358Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
@@ -1850,7 +1850,7 @@
     <t>Verify a change above 1% needs acknowledgement before checkout.</t>
   </si>
   <si>
-    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate rises 30% after the cart is created.</t>
+    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate is 200 when the cart is created and rises 30% to 260.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Create a cart
@@ -1876,7 +1876,7 @@
     <t>Verify a change within 1% is applied without blocking the guest.</t>
   </si>
   <si>
-    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate rises 0.5% after the cart is created.</t>
+    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate is 200 when the cart is created and rises 0.5% to 201.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Create a cart
@@ -2993,7 +2993,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-12T01:35:49.358Z</t>
+    <t>2026-10-12T02:10:48.865Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
@@ -2993,7 +2993,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-12T02:10:48.865Z</t>
+    <t>2026-10-12T02:22:46.709Z</t>
   </si>
   <si>
     <t>Column order</t>
